--- a/两国军事单位初步设计.xlsx
+++ b/两国军事单位初步设计.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OMEN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\私人物品\-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0A3B67-9B23-47BD-82DE-C4E2F51F4E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9432F78E-91C7-492B-819C-8CD40A1AE936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{59B0A9D9-1E99-423F-90EC-2ECFF22B4B2C}"/>
   </bookViews>
@@ -179,10 +179,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>什么是火药？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>越野步兵</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -227,10 +223,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>火门枪+攻城火炮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">长刀兵 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -244,6 +236,14 @@
   </si>
   <si>
     <t>在广阔的疆域里，远水解不了近渴。耐力优秀、擅长快速且远程行军的士兵永远不嫌多。别问为什么不骑马，因为养马真的很麻烦。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旧大战的胜利者还沉浸在胜利的光环当中，丝毫没有注意到时代的变革已经到来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火门枪/攻城火炮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -303,7 +303,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -422,13 +422,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -464,6 +482,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -818,10 +842,10 @@
         <v>4</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="62" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -863,7 +887,7 @@
         <v>28</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>7</v>
@@ -897,7 +921,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>9</v>
@@ -910,54 +934,54 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="62" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>35</v>
+      <c r="A9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="62" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="62" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="94" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -965,16 +989,16 @@
         <v>22</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
